--- a/xls/square_un_16_tri3_19.xlsx
+++ b/xls/square_un_16_tri3_19.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>485</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>340</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>380</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>2070</v>
+      </c>
+      <c r="I17">
+        <v>-0.0001851884976603905</v>
+      </c>
+      <c r="J17">
+        <v>-0.871390711096769</v>
+      </c>
+      <c r="K17">
+        <v>2.146387909984021</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>485</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>340</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>435</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>2388</v>
+      </c>
+      <c r="I18">
+        <v>-0.0001339143184603637</v>
+      </c>
+      <c r="J18">
+        <v>-0.4923234307043094</v>
+      </c>
+      <c r="K18">
+        <v>2.543195339149446</v>
+      </c>
+    </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>11</v>
       </c>
       <c r="B19">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-2.371062811328965</v>
+        <v>-5.0922920651138975e-5</v>
       </c>
       <c r="J19">
-        <v>-2.24944322983498</v>
+        <v>-0.15502249698490714</v>
       </c>
       <c r="K19">
-        <v>-0.2763248878032458</v>
+        <v>3.2351608601618946</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-2.5203250798952452</v>
+        <v>-4.8964156589357787e-8</v>
       </c>
       <c r="J20">
-        <v>-2.1988742492595614</v>
+        <v>-9.52149213398529e-5</v>
       </c>
       <c r="K20">
-        <v>0.15165432452181726</v>
+        <v>2.415489181154829</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-2.006370749032557</v>
+        <v>-1.8064395887870188e-8</v>
       </c>
       <c r="J21">
-        <v>-1.622066623153358</v>
+        <v>-3.536310359868957e-5</v>
       </c>
       <c r="K21">
-        <v>1.4431626223282619</v>
+        <v>2.2082340638439386</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-0.7638865683054556</v>
+        <v>-6.660601665775587e-9</v>
       </c>
       <c r="J22">
-        <v>-0.6517198243665785</v>
+        <v>-1.1882686025028454e-5</v>
       </c>
       <c r="K22">
-        <v>3.0955269546856985</v>
+        <v>1.9674586895064266</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-0.007817081139439363</v>
+        <v>-3.6334863905778587e-9</v>
       </c>
       <c r="J23">
-        <v>-0.011698690497734983</v>
+        <v>-6.371424754042953e-6</v>
       </c>
       <c r="K23">
-        <v>3.402439097156916</v>
+        <v>1.8349832335317524</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-0.0005789825363774956</v>
+        <v>-2.4326925613367607e-9</v>
       </c>
       <c r="J24">
-        <v>-0.0008200363610850978</v>
+        <v>-4.712351390131397e-6</v>
       </c>
       <c r="K24">
-        <v>2.9678673514667677</v>
+        <v>1.7782603380268653</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-0.00025613140182837867</v>
+        <v>-1.4978762593630208e-9</v>
       </c>
       <c r="J25">
-        <v>-0.0003323120180187806</v>
+        <v>-3.0235248390325307e-6</v>
       </c>
       <c r="K25">
-        <v>2.7681364812453</v>
+        <v>1.6872466766342247</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-0.0001272925584655137</v>
+        <v>-1.408952537526656e-9</v>
       </c>
       <c r="J26">
-        <v>-0.000156696932929817</v>
+        <v>-2.7516053507782045e-6</v>
       </c>
       <c r="K26">
-        <v>2.598861151437619</v>
+        <v>1.665209879742183</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-7.946101190484991e-5</v>
+        <v>-1.1206795696835586e-9</v>
       </c>
       <c r="J27">
-        <v>-0.00010202208103104084</v>
+        <v>-2.1917070669135197e-6</v>
       </c>
       <c r="K27">
-        <v>2.5099469903200498</v>
+        <v>1.6160522136085251</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-5.567338262941146e-5</v>
+        <v>-1.1598672825593881e-9</v>
       </c>
       <c r="J28">
-        <v>-6.75940227293081e-5</v>
+        <v>-2.369581418137842e-6</v>
       </c>
       <c r="K28">
-        <v>2.4117185687367044</v>
+        <v>1.6374176912171694</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-4.6838991237009555e-5</v>
+        <v>-1.1725502620826745e-9</v>
       </c>
       <c r="J29">
-        <v>-5.861120743010573e-5</v>
+        <v>-2.2542113524552748e-6</v>
       </c>
       <c r="K29">
-        <v>2.3853114631861745</v>
+        <v>1.6210794626738048</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-3.8815592163227524e-5</v>
+        <v>-8.353820826519457e-10</v>
       </c>
       <c r="J30">
-        <v>-4.679283070194164e-5</v>
+        <v>-1.6339752262107279e-6</v>
       </c>
       <c r="K30">
-        <v>2.3297751926951666</v>
+        <v>1.5532263811299538</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-2.8330354394824076e-5</v>
+        <v>-7.199410913656862e-10</v>
       </c>
       <c r="J31">
-        <v>-3.5264860726745906e-5</v>
+        <v>-1.3828772332907343e-6</v>
       </c>
       <c r="K31">
-        <v>2.275300929656492</v>
+        <v>1.5161789387142626</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -916,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-2.4920272660480835e-5</v>
+        <v>-7.094672414359745e-10</v>
       </c>
       <c r="J32">
-        <v>-3.0676119502693164e-5</v>
+        <v>-1.404445291313065e-6</v>
       </c>
       <c r="K32">
-        <v>2.242225582726044</v>
+        <v>1.5225093389013202</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_19.xlsx
+++ b/xls/square_un_16_tri3_19.xlsx
@@ -482,13 +482,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-0.0001851884976603905</v>
+        <v>-1.9194402020127486</v>
       </c>
       <c r="J17">
-        <v>-0.871390711096769</v>
+        <v>-1.9738014380523425</v>
       </c>
       <c r="K17">
-        <v>2.146387909984021</v>
+        <v>-0.6992408083410955</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-0.0001339143184603637</v>
+        <v>-2.3178649284607094</v>
       </c>
       <c r="J18">
-        <v>-0.4923234307043094</v>
+        <v>-1.848882330076526</v>
       </c>
       <c r="K18">
-        <v>2.543195339149446</v>
+        <v>0.2018518571308959</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-5.0922920651138975e-5</v>
+        <v>-1.3986733144403887</v>
       </c>
       <c r="J19">
-        <v>-0.15502249698490714</v>
+        <v>-1.2183487247066198</v>
       </c>
       <c r="K19">
-        <v>3.2351608601618946</v>
+        <v>1.1305853911633115</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-4.8964156589357787e-8</v>
+        <v>-0.010266764867842513</v>
       </c>
       <c r="J20">
-        <v>-9.52149213398529e-5</v>
+        <v>-0.0105112826106345</v>
       </c>
       <c r="K20">
-        <v>2.415489181154829</v>
+        <v>2.9307719828579315</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.8064395887870188e-8</v>
+        <v>0.00010021986483718059</v>
       </c>
       <c r="J21">
-        <v>-3.536310359868957e-5</v>
+        <v>-9.240131398974374e-5</v>
       </c>
       <c r="K21">
-        <v>2.2082340638439386</v>
+        <v>2.628281516651553</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-6.660601665775587e-9</v>
+        <v>-1.1893612840685406e-5</v>
       </c>
       <c r="J22">
-        <v>-1.1882686025028454e-5</v>
+        <v>-1.3858847017195843e-5</v>
       </c>
       <c r="K22">
-        <v>1.9674586895064266</v>
+        <v>2.050925251759771</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-3.6334863905778587e-9</v>
+        <v>-4.850422322742627e-6</v>
       </c>
       <c r="J23">
-        <v>-6.371424754042953e-6</v>
+        <v>-6.2022593455977614e-6</v>
       </c>
       <c r="K23">
-        <v>1.8349832335317524</v>
+        <v>1.8931046593606227</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-2.4326925613367607e-9</v>
+        <v>-5.004309391636455e-6</v>
       </c>
       <c r="J24">
-        <v>-4.712351390131397e-6</v>
+        <v>-5.211291983786793e-6</v>
       </c>
       <c r="K24">
-        <v>1.7782603380268653</v>
+        <v>1.8138732235329187</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-1.4978762593630208e-9</v>
+        <v>-4.52410880098344e-6</v>
       </c>
       <c r="J25">
-        <v>-3.0235248390325307e-6</v>
+        <v>-4.187405827627665e-6</v>
       </c>
       <c r="K25">
-        <v>1.6872466766342247</v>
+        <v>1.7364428642294154</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-1.408952537526656e-9</v>
+        <v>-2.8054213167949003e-6</v>
       </c>
       <c r="J26">
-        <v>-2.7516053507782045e-6</v>
+        <v>-2.9124525124194314e-6</v>
       </c>
       <c r="K26">
-        <v>1.665209879742183</v>
+        <v>1.6890809253695651</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-1.1206795696835586e-9</v>
+        <v>-2.6104220152722537e-6</v>
       </c>
       <c r="J27">
-        <v>-2.1917070669135197e-6</v>
+        <v>-2.542436775178712e-6</v>
       </c>
       <c r="K27">
-        <v>1.6160522136085251</v>
+        <v>1.6438153946953935</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-1.1598672825593881e-9</v>
+        <v>-2.4862058542540615e-6</v>
       </c>
       <c r="J28">
-        <v>-2.369581418137842e-6</v>
+        <v>-2.5604359754567475e-6</v>
       </c>
       <c r="K28">
-        <v>1.6374176912171694</v>
+        <v>1.656447852676048</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -902,13 +902,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-1.1725502620826745e-9</v>
+        <v>-3.10804426021303e-6</v>
       </c>
       <c r="J29">
-        <v>-2.2542113524552748e-6</v>
+        <v>-2.7995520456501794e-6</v>
       </c>
       <c r="K29">
-        <v>1.6210794626738048</v>
+        <v>1.6397840793709741</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -937,13 +937,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-8.353820826519457e-10</v>
+        <v>-2.0837522668408785e-6</v>
       </c>
       <c r="J30">
-        <v>-1.6339752262107279e-6</v>
+        <v>-1.961270606321065e-6</v>
       </c>
       <c r="K30">
-        <v>1.5532263811299538</v>
+        <v>1.575581503778842</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -972,13 +972,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-7.199410913656862e-10</v>
+        <v>-1.8384504831909544e-6</v>
       </c>
       <c r="J31">
-        <v>-1.3828772332907343e-6</v>
+        <v>-1.6900364316150724e-6</v>
       </c>
       <c r="K31">
-        <v>1.5161789387142626</v>
+        <v>1.537841355877965</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-7.094672414359745e-10</v>
+        <v>-1.7312022386483543e-6</v>
       </c>
       <c r="J32">
-        <v>-1.404445291313065e-6</v>
+        <v>-1.6370628080683398e-6</v>
       </c>
       <c r="K32">
-        <v>1.5225093389013202</v>
+        <v>1.5381666815377697</v>
       </c>
     </row>
   </sheetData>
